--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0018.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0018.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Ra là vậy...</t>
+          <t>Ta hiểu rồi...</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Ta sẽ đi tìm bác sĩ cho cậu.</t>
+          <t>Tao sẽ đi tìm bác sĩ cho cậu.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Đợi Wuli tỉnh dậy, ta sẽ giải thích hết mọi chuyện cho nó.</t>
+          <t>Đợi Wuli tỉnh dậy, tao sẽ giải thích hết mọi chuyện cho nó.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>...Vâng. Ta hiểu rồi.</t>
+          <t>...Vâng. Tao hiểu rồi.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Cậu biết chuyện này từ trước rồi à?</t>
+          <t>Mày biết chuyện này từ trước rồi à?</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Ngươi muốn gì? Ta đâu có làm gì sai!</t>
+          <t>Mày muốn gì? Tao đâu có làm gì sai!</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Sao lại thế?</t>
+          <t>Sao cơ?</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Hừ... Ta nói ngươi đang đánh giá thấp mưu mẹo của Changli đấy.</t>
+          <t>Hừ... Tao nói mày đang đánh giá thấp mưu mẹo của Changli đấy.</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Hóa ra từ bao năm trước ta đã gặp cậu rồi, ân nhân của đời ta... mà cậu lại lớn tuổi hơn ta. Lẽ ra hồi đó ta phải tôn trọng cậu hơn mới phải.</t>
+          <t>Hóa ra từ bao năm trước tao đã gặp cậu rồi, ân nhân của đời tao... mà cậu lại lớn tuổi hơn tao. Lẽ ra hồi đó tao phải tôn trọng cậu hơn mới phải.</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Thế à? Chẳng phải sẽ rất ngoạn mục sao, khi Quả Cầu Sonoro này nuốt chửng mọi thứ trên đường đi, còn những Rối Loạn Thời Gian mang đến cái chết?</t>
+          <t>Thế à? Chẳng phải sẽ rất ngoạn mục sao, khi Sonoro Sphere này nuốt chửng mọi thứ trên đường đi, còn những Rối Loạn Thời Gian mang đến cái chết?</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Ơ... Sao cô ấy biến mất nhanh thế? Khoan, ông chính là Rover huyền thoại đã cứu Jinzhou à?!</t>
+          <t>Ơ... Sao cô ấy biến mất nhanh thế? Khoan, ông chính là Vận Mệnh Giả huyền thoại đã cứu Jinzhou à?!</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>"Bên cạnh chiếc vòng và mái hiên treo"... Ồ! Tớ biết chỗ đó rồi. Cậu sẽ cần đứng trên tòa nhà cao nhất ở Hồng Trấn để thấy thứ mình cần tìm."</t>
+          <t>"Bên cạnh chiếc vòng và mái hiên treo"... Ồ! Tớ biết chỗ đó rồi. Cậu sẽ cần đứng trên tòa nhà cao nhất ở Hongzhen để thấy thứ mình cần tìm."</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Thật sao?</t>
+          <t>Thật chứ?</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>"Gặp nhau ở nơi cao nhất Hồng Trấn vào đầu giờ chiều nhé."</t>
+          <t>"Gặp nhau ở nơi cao nhất Hongzhen vào đầu giờ chiều nhé."</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Chúng tôi mang ơn Rover rất nhiều vì những nỗ lực dọn dẹp hậu quả của Temporal Disruptions tại Núi Firmament trong mấy ngày qua.</t>
+          <t>Chúng tôi mang ơn Vận Mệnh Giả rất nhiều vì những nỗ lực dọn dẹp hậu quả của Temporal Disruptions tại Núi Firmament trong mấy ngày qua.</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Công việc đó đúng là ác mộng. Tiền của ta phải sẵn sàng đấy.</t>
+          <t>Công việc đó đúng là ác mộng. Tiền của tao phải sẵn sàng đấy.</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Ta nghĩ tốt hơn là để cô ấy tự kể với ngươi.</t>
+          <t>Tao nghĩ tốt hơn là để cô ấy tự kể với mày.</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Sự Rối Loạn Thời Gian ẩn trong một Quả Cầu Sonoro... Giờ thì ta hiểu tại sao nó lại lẩn trốn được lâu đến vậy.</t>
+          <t>Sự Rối Loạn Thời Gian ẩn trong một Sonoro Sphere... Giờ thì ta hiểu tại sao nó lại lẩn trốn được lâu đến vậy.</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Tôi chưa từng cảm ơn cậu một cách tử tế vì đã đưa tôi trở lại Hồng Trấn. Tôi nghe nói về cuộc tấn công của Fractsidus trên núi... Tôi... thật sự xin lỗi...</t>
+          <t>Tôi chưa từng cảm ơn cậu một cách tử tế vì đã đưa tôi trở lại Hongzhen. Tôi nghe nói về cuộc tấn công của Fractsidus trên núi... Tôi... thật sự xin lỗi...</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Ta biết ngươi đã vượt qua cả cái chết, nhưng hãy nhớ... vẫn còn những người quan tâm đến ngươi. Họ muốn ngươi sống tiếp và hạnh phúc.</t>
+          <t>Tao biết mày đã vượt qua cả cái chết, nhưng hãy nhớ... vẫn còn những người quan tâm đến mày. Họ muốn mày sống tiếp và hạnh phúc.</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Ôi. Cậu không thấy em ngồi đây khỏe re đấy thôi à?</t>
+          <t>Ôi. bạn không thấy em ngồi đây khỏe re đấy thôi à?</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Được thôi, hỏi đi. Ta sẽ trả lời hết sức có thể.</t>
+          <t>Được thôi, hỏi đi. Tao sẽ trả lời hết sức có thể.</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Về Quả Cầu Sonoro...</t>
+          <t>Về Sonoro Sphere...</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Sau khi sư phụ qua đời, {Male=anh ấy;Female=cô ấy} sẽ là người duy nhất có thể điều khiển Quả Cầu Sonoro. Đến giờ, chắc cậu cũng biết {Male=anh ấy;Female=cô ấy} là ai rồi.</t>
+          <t>Sau khi sư phụ qua đời, {Male=he;Female=she} sẽ là người duy nhất có thể điều khiển Sonoro Sphere. Đến giờ, chắc cậu cũng biết {Male=he;Female=she} là ai rồi.</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Ta nghĩ là ta.</t>
+          <t>Tao nghĩ là tao.</t>
         </is>
       </c>
     </row>
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Chính vì thế mà cậu mới cần ta làm Người Dẫn Đường cho cậu.</t>
+          <t>Chính vì thế mà cậu mới cần tao làm Người Dẫn Đường cho cậu.</t>
         </is>
       </c>
     </row>
@@ -21894,7 +21894,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Tất nhiên rồi.</t>
+          <t>Đương nhiên.</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Ra là vậy...</t>
+          <t>Ta hiểu rồi...</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Ta có cảm giác cậu đã ở đây được một thời gian rồi.</t>
+          <t>Tao có cảm giác cậu đã ở đây được một thời gian rồi.</t>
         </is>
       </c>
     </row>
@@ -24949,7 +24949,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Xin lỗi vì đã để cậu có ấn tượng đó, Rover. Chúng tôi không đối xử với ân nhân của mình như vậy đâu.</t>
+          <t>Xin lỗi vì đã để cậu có ấn tượng đó, Vận Mệnh Giả. Chúng tôi không đối xử với ân nhân của mình như vậy đâu.</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Xin lỗi vì đã để cậu có ấn tượng đó, Rover. Chúng tôi không đối xử với ân nhân của mình như vậy đâu.</t>
+          <t>Xin lỗi vì đã để cậu có ấn tượng đó, Vận Mệnh Giả. Chúng tôi không đối xử với ân nhân của mình như vậy đâu.</t>
         </is>
       </c>
     </row>
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Ván &lt;ano=Go&gt;Cờ vây&lt;/ano&gt; này có quen thuộc với cậu không, Rover?</t>
+          <t>Ván &lt;ano=Go&gt;Cờ vây&lt;/ano&gt; này có quen thuộc với cậu không, Vận Mệnh Giả?</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Là cái giọng mình nghe được ở Hồng Trấn ấy à?</t>
+          <t>Là cái giọng mình nghe được ở Hongzhen ấy à?</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Được rồi. Gặp nhau ở con đường trưng bày ngoài Hồng Trấn nhé.</t>
+          <t>Được rồi. Gặp nhau ở con đường trưng bày ngoài Hongzhen nhé.</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Hồng Trấn quả là một nơi thư giãn dễ chịu.</t>
+          <t>Hongzhen quả là một nơi thư giãn dễ chịu.</t>
         </is>
       </c>
     </row>
@@ -31189,7 +31189,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Cậu ổn chứ?</t>
+          <t>Cậu ổn không?</t>
         </is>
       </c>
     </row>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Ngươi... Tránh xa ta ra, không ta sẽ thiêu rụi ngươi.</t>
+          <t>Mày... Tránh xa tao ra, không tao sẽ thiêu rụi mày.</t>
         </is>
       </c>
     </row>
